--- a/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q100_LO.xlsx
+++ b/Main/AUT_EEC_results/AUT_EEC_SIDIS_a0.01_b0.01_x0.10_Q100_LO.xlsx
@@ -455,10 +455,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0.009437304159295754</v>
+        <v>0.008349596029912365</v>
       </c>
       <c r="C2" t="n">
-        <v>0.009437304159295754</v>
+        <v>0.008349596029912365</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
@@ -469,10 +469,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02560851283552388</v>
+        <v>0.02325117257752361</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02560851283552388</v>
+        <v>0.02325117257752361</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -483,10 +483,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0.05334595895599677</v>
+        <v>0.04826128040757328</v>
       </c>
       <c r="C4" t="n">
-        <v>0.05334595895599677</v>
+        <v>0.04826128040757328</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -497,10 +497,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0.07228361635282916</v>
+        <v>0.06549498261744116</v>
       </c>
       <c r="C5" t="n">
-        <v>0.07228361635282916</v>
+        <v>0.06549498261744116</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -511,10 +511,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>0.06970058792268939</v>
+        <v>0.06303124321499375</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06970058792268939</v>
+        <v>0.06303124321499375</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -525,10 +525,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>0.06256520739943615</v>
+        <v>0.05665019169591694</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06256520739943615</v>
+        <v>0.05665019169591694</v>
       </c>
       <c r="D7" t="n">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>0.05640814118167838</v>
+        <v>0.05118102260680845</v>
       </c>
       <c r="C8" t="n">
-        <v>0.05640814118167838</v>
+        <v>0.05118102260680845</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
@@ -553,10 +553,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>0.0526119976815646</v>
+        <v>0.04776119596994949</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0526119976815646</v>
+        <v>0.04776119596994949</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
